--- a/analysis/aggregate/set-PRF.xlsx
+++ b/analysis/aggregate/set-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y9"/>
+  <dimension ref="A1:Y17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,7 +551,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -578,58 +578,58 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6142633067767237</v>
+        <v>0.5903033345801358</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01707452577899938</v>
+        <v>0.008589468757146553</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5847058823529412</v>
       </c>
       <c r="K2" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.007892004626469874</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6093984433885951</v>
+        <v>0.5874734570806145</v>
       </c>
       <c r="M2" t="n">
-        <v>0.01406682628532503</v>
+        <v>0.007402257362222917</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6234159779614326</v>
+        <v>0.603305785123967</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01386334726180294</v>
+        <v>0.01097615526894569</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6214876033057851</v>
+        <v>0.6022038567493113</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.01206315925389064</v>
+        <v>0.009661530532644701</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6191735537190083</v>
+        <v>0.598181818181818</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01272834598887834</v>
+        <v>0.01028843561989865</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6170588235294118</v>
+        <v>0.5966666666666667</v>
       </c>
       <c r="U2" t="n">
-        <v>0.01305431824774831</v>
+        <v>0.009264576199943111</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5847058823529412</v>
       </c>
       <c r="W2" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.007892004626469874</v>
       </c>
       <c r="X2" t="n">
-        <v>0.6069803921568627</v>
+        <v>0.5853333333333334</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.01262659843669335</v>
+        <v>0.008395271549546149</v>
       </c>
     </row>
     <row r="3">
@@ -640,7 +640,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -667,58 +667,58 @@
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6142633067767237</v>
+        <v>0.5743588344908772</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01707452577899938</v>
+        <v>0.01725819660056498</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01764705882352943</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6093984433885951</v>
+        <v>0.5664772405168468</v>
       </c>
       <c r="M3" t="n">
-        <v>0.01406682628532503</v>
+        <v>0.0173152532875685</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6234159779614326</v>
+        <v>0.5877410468319559</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01386334726180294</v>
+        <v>0.01838726897627025</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6214876033057851</v>
+        <v>0.5771349862258953</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01206315925389064</v>
+        <v>0.01573506840054526</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6191735537190083</v>
+        <v>0.5732546241637151</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01272834598887834</v>
+        <v>0.01689606040553305</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6170588235294118</v>
+        <v>0.5928431372549019</v>
       </c>
       <c r="U3" t="n">
-        <v>0.01305431824774831</v>
+        <v>0.02243577702541934</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5588235294117647</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01764705882352943</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6069803921568627</v>
+        <v>0.5637927170868349</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01262659843669335</v>
+        <v>0.01958351431853349</v>
       </c>
     </row>
     <row r="4">
@@ -729,7 +729,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -756,58 +756,58 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6191060050431599</v>
+        <v>0.5746979265078813</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0146911284029345</v>
+        <v>0.01671098573689573</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5705882352941176</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.01440876319284219</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6123924381339001</v>
+        <v>0.5726329050759436</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01195812108222937</v>
+        <v>0.01552630722297881</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6123966942148761</v>
+        <v>0.5763085399449037</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0124957778843435</v>
+        <v>0.02132985821933815</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6090909090909091</v>
+        <v>0.5694214876033058</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.01300905669765022</v>
+        <v>0.02101623264216045</v>
       </c>
       <c r="R4" t="n">
-        <v>0.606831955922865</v>
+        <v>0.5685399449035812</v>
       </c>
       <c r="S4" t="n">
-        <v>0.01189910455862876</v>
+        <v>0.02099672399025554</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6209803921568626</v>
+        <v>0.5888235294117646</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0123350321470993</v>
+        <v>0.01674721022634053</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5705882352941176</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.01440876319284219</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6087058823529412</v>
+        <v>0.5742745098039215</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01055331933656936</v>
+        <v>0.01560419703199935</v>
       </c>
     </row>
     <row r="5">
@@ -818,7 +818,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -845,58 +845,58 @@
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6191060050431599</v>
+        <v>0.5518064396027279</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0146911284029345</v>
+        <v>0.0197235328887144</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5388235294117647</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.02020654592625613</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6123924381339001</v>
+        <v>0.5452236165817694</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01195812108222937</v>
+        <v>0.01971884177259502</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6123966942148761</v>
+        <v>0.5668044077134986</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0124957778843435</v>
+        <v>0.02190364172698239</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6090909090909091</v>
+        <v>0.5476584022038569</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.01300905669765022</v>
+        <v>0.02453569788125821</v>
       </c>
       <c r="R5" t="n">
-        <v>0.606831955922865</v>
+        <v>0.5491223927587564</v>
       </c>
       <c r="S5" t="n">
-        <v>0.01189910455862876</v>
+        <v>0.02276992476299774</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6209803921568626</v>
+        <v>0.5799019607843137</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0123350321470993</v>
+        <v>0.01954954568883272</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.5388235294117647</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.02020654592625613</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6087058823529412</v>
+        <v>0.5479495798319328</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.01055331933656936</v>
+        <v>0.0192602076293441</v>
       </c>
     </row>
     <row r="6">
@@ -907,7 +907,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -931,61 +931,61 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6142652596272505</v>
+        <v>0.6015430354997375</v>
       </c>
       <c r="I6" t="n">
-        <v>0.008051003944109524</v>
+        <v>0.02233941822238216</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6088235294117647</v>
+        <v>0.5894117647058824</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01018853416216988</v>
+        <v>0.0192416790985837</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6115091512764134</v>
+        <v>0.5954038321822781</v>
       </c>
       <c r="M6" t="n">
-        <v>0.00811196840080511</v>
+        <v>0.02060234514657168</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6294765840220385</v>
+        <v>0.6170798898071624</v>
       </c>
       <c r="O6" t="n">
-        <v>0.004637054608981692</v>
+        <v>0.01370506111717106</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6336088154269972</v>
+        <v>0.6082644628099173</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.007023442856188429</v>
+        <v>0.01716520945418665</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6284435261707988</v>
+        <v>0.6089256198347106</v>
       </c>
       <c r="S6" t="n">
-        <v>0.005286457592946406</v>
+        <v>0.01503031918760192</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6105392156862746</v>
+        <v>0.6094117647058823</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01116026229838511</v>
+        <v>0.01642851769855169</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6088235294117647</v>
+        <v>0.5894117647058824</v>
       </c>
       <c r="W6" t="n">
-        <v>0.01018853416216988</v>
+        <v>0.0192416790985837</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6064705882352941</v>
+        <v>0.5943529411764705</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.009756749258529211</v>
+        <v>0.0177325814376939</v>
       </c>
     </row>
     <row r="7">
@@ -996,7 +996,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1023,58 +1023,58 @@
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6161180900547416</v>
+        <v>0.6015430354997375</v>
       </c>
       <c r="I7" t="n">
-        <v>0.008110419307670447</v>
+        <v>0.02233941822238216</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6117647058823529</v>
+        <v>0.5894117647058824</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01100487466698223</v>
+        <v>0.0192416790985837</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6139132033740718</v>
+        <v>0.5954038321822781</v>
       </c>
       <c r="M7" t="n">
-        <v>0.008845923125543572</v>
+        <v>0.02060234514657168</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6314049586776859</v>
+        <v>0.6170798898071624</v>
       </c>
       <c r="O7" t="n">
-        <v>0.005892355271682484</v>
+        <v>0.01370506111717106</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6347107438016528</v>
+        <v>0.6082644628099173</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.006562605647146912</v>
+        <v>0.01716520945418665</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6297520661157023</v>
+        <v>0.6089256198347106</v>
       </c>
       <c r="S7" t="n">
-        <v>0.005433356177222039</v>
+        <v>0.01503031918760192</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6149019607843137</v>
+        <v>0.6094117647058823</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0137324912116809</v>
+        <v>0.01642851769855169</v>
       </c>
       <c r="V7" t="n">
-        <v>0.6117647058823529</v>
+        <v>0.5894117647058824</v>
       </c>
       <c r="W7" t="n">
-        <v>0.01100487466698223</v>
+        <v>0.0192416790985837</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6098823529411764</v>
+        <v>0.5943529411764705</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.01138403746971526</v>
+        <v>0.0177325814376939</v>
       </c>
     </row>
     <row r="8">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1112,58 +1112,58 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6204715166401845</v>
+        <v>0.5923053929249383</v>
       </c>
       <c r="I8" t="n">
-        <v>0.008102275685873442</v>
+        <v>0.01382262782588121</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6094117647058823</v>
+        <v>0.5894117647058824</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00526133641764661</v>
+        <v>0.01131493180098317</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6148484005176831</v>
+        <v>0.5908235870407339</v>
       </c>
       <c r="M8" t="n">
-        <v>0.003568416526102522</v>
+        <v>0.01168310669472389</v>
       </c>
       <c r="N8" t="n">
-        <v>0.6104683195592286</v>
+        <v>0.5994490358126722</v>
       </c>
       <c r="O8" t="n">
-        <v>0.008623953632230612</v>
+        <v>0.01112210977310539</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6115702479338843</v>
+        <v>0.5925619834710745</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01148301101965086</v>
+        <v>0.01229681218769456</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6069500196772923</v>
+        <v>0.5916804407713498</v>
       </c>
       <c r="S8" t="n">
-        <v>0.008627302351816017</v>
+        <v>0.01133400427375002</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6168627450980392</v>
+        <v>0.608235294117647</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01183394657020111</v>
+        <v>0.01177695440819236</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6094117647058823</v>
+        <v>0.5894117647058824</v>
       </c>
       <c r="W8" t="n">
-        <v>0.00526133641764661</v>
+        <v>0.01131493180098317</v>
       </c>
       <c r="X8" t="n">
-        <v>0.6087226890756302</v>
+        <v>0.5929803921568627</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.005750271159191041</v>
+        <v>0.01096935720020186</v>
       </c>
     </row>
     <row r="9">
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1201,57 +1201,769 @@
         <v>5</v>
       </c>
       <c r="H9" t="n">
+        <v>0.5923053929249383</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.01382262782588121</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.5894117647058824</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.01131493180098317</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5908235870407339</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01168310669472389</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.5994490358126722</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.01112210977310539</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.5925619834710745</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01229681218769456</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5916804407713498</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.01133400427375002</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.608235294117647</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.01177695440819236</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.5894117647058824</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.01131493180098317</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.5929803921568627</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.01096935720020186</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.6142633067767237</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.01707452577899938</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6047058823529412</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.01341382853057812</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6093984433885951</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.01406682628532503</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.6234159779614326</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.01386334726180294</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.6214876033057851</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.01206315925389064</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.6191735537190083</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.01272834598887834</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6170588235294118</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.01305431824774831</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.6047058823529412</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.01341382853057812</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.6069803921568627</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.01262659843669335</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6142633067767237</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.01707452577899938</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6047058823529412</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01341382853057812</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6093984433885951</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.01406682628532503</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.6234159779614326</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.01386334726180294</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.6214876033057851</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.01206315925389064</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.6191735537190083</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.01272834598887834</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.6170588235294118</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.01305431824774831</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.6047058823529412</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.01341382853057812</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.6069803921568627</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.01262659843669335</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.6191060050431599</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.0146911284029345</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0110048746669822</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6123924381339001</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.01195812108222937</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6123966942148761</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0124957778843435</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.6090909090909091</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.01300905669765022</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.606831955922865</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.01189910455862876</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.6209803921568626</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.0123350321470993</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.0110048746669822</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.6087058823529412</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.01055331933656936</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6191060050431599</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.0146911284029345</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0110048746669822</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6123924381339001</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01195812108222937</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6123966942148761</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.0124957778843435</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.6090909090909091</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.01300905669765022</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.606831955922865</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.01189910455862876</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.6209803921568626</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.0123350321470993</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.6058823529411764</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.0110048746669822</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.6087058823529412</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.01055331933656936</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>4</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.6142652596272505</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.008051003944109524</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6088235294117647</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01018853416216988</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6115091512764134</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.00811196840080511</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.6294765840220385</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.004637054608981692</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.6336088154269972</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.007023442856188429</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.6284435261707988</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.005286457592946406</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.6105392156862746</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.01116026229838511</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0.6088235294117647</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0.01018853416216988</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.6064705882352941</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.009756749258529211</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.6161180900547416</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.008110419307670447</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.6117647058823529</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.01100487466698223</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6139132033740718</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.008845923125543572</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6314049586776859</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.005892355271682484</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.6347107438016528</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.006562605647146912</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.6297520661157023</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.005433356177222039</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.6149019607843137</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.0137324912116809</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.6117647058823529</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0.01100487466698223</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.6098823529411764</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.01138403746971526</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>5</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.6204715166401845</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I16" t="n">
         <v>0.008102275685873442</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J16" t="n">
         <v>0.6094117647058823</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K16" t="n">
         <v>0.00526133641764661</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L16" t="n">
         <v>0.6148484005176831</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M16" t="n">
         <v>0.003568416526102522</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N16" t="n">
         <v>0.6104683195592286</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O16" t="n">
         <v>0.008623953632230612</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P16" t="n">
         <v>0.6115702479338843</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="Q16" t="n">
         <v>0.01148301101965086</v>
       </c>
-      <c r="R9" t="n">
+      <c r="R16" t="n">
         <v>0.6069500196772923</v>
       </c>
-      <c r="S9" t="n">
+      <c r="S16" t="n">
         <v>0.008627302351816017</v>
       </c>
-      <c r="T9" t="n">
+      <c r="T16" t="n">
         <v>0.6168627450980392</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U16" t="n">
         <v>0.01183394657020111</v>
       </c>
-      <c r="V9" t="n">
+      <c r="V16" t="n">
         <v>0.6094117647058823</v>
       </c>
-      <c r="W9" t="n">
+      <c r="W16" t="n">
         <v>0.00526133641764661</v>
       </c>
-      <c r="X9" t="n">
+      <c r="X16" t="n">
         <v>0.6087226890756302</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y16" t="n">
+        <v>0.005750271159191041</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6204715166401845</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.008102275685873442</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.6094117647058823</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.00526133641764661</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6148484005176831</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.003568416526102522</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.6104683195592286</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.008623953632230612</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.6115702479338843</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.01148301101965086</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.6069500196772923</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.008627302351816017</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.6168627450980392</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.01183394657020111</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.6094117647058823</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0.00526133641764661</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.6087226890756302</v>
+      </c>
+      <c r="Y17" t="n">
         <v>0.005750271159191041</v>
       </c>
     </row>

--- a/analysis/aggregate/set-PRF.xlsx
+++ b/analysis/aggregate/set-PRF.xlsx
@@ -561,7 +561,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -578,58 +578,58 @@
         <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5903033345801358</v>
+        <v>0.5936375229711428</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008589468757146553</v>
+        <v>0.01858140208562855</v>
       </c>
       <c r="J2" t="n">
-        <v>0.5847058823529412</v>
+        <v>0.5835294117647059</v>
       </c>
       <c r="K2" t="n">
-        <v>0.007892004626469874</v>
+        <v>0.006443794794178469</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5874734570806145</v>
+        <v>0.5884727954748277</v>
       </c>
       <c r="M2" t="n">
-        <v>0.007402257362222917</v>
+        <v>0.01177885648413864</v>
       </c>
       <c r="N2" t="n">
-        <v>0.603305785123967</v>
+        <v>0.6115702479338843</v>
       </c>
       <c r="O2" t="n">
-        <v>0.01097615526894569</v>
+        <v>0.009884779679343874</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6022038567493113</v>
+        <v>0.6090909090909091</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.009661530532644701</v>
+        <v>0.006489927817845653</v>
       </c>
       <c r="R2" t="n">
-        <v>0.598181818181818</v>
+        <v>0.6066666666666666</v>
       </c>
       <c r="S2" t="n">
-        <v>0.01028843561989865</v>
+        <v>0.008760157317620631</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5966666666666667</v>
+        <v>0.5954901960784313</v>
       </c>
       <c r="U2" t="n">
-        <v>0.009264576199943111</v>
+        <v>0.01010802856375062</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5847058823529412</v>
+        <v>0.5835294117647059</v>
       </c>
       <c r="W2" t="n">
-        <v>0.007892004626469874</v>
+        <v>0.006443794794178469</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5853333333333334</v>
+        <v>0.5850196078431372</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.008395271549546149</v>
+        <v>0.008633687585416133</v>
       </c>
     </row>
     <row r="3">
@@ -650,75 +650,75 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>5</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5743588344908772</v>
+        <v>0.5888346412660498</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01725819660056498</v>
+        <v>0.01230538090355283</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.5776470588235294</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01764705882352943</v>
+        <v>0.008724939396583146</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5664772405168468</v>
+        <v>0.5831588438986696</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0173152532875685</v>
+        <v>0.009579076578811369</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5877410468319559</v>
+        <v>0.5887052341597796</v>
       </c>
       <c r="O3" t="n">
-        <v>0.01838726897627025</v>
+        <v>0.01504470239219079</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5771349862258953</v>
+        <v>0.5809917355371901</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.01573506840054526</v>
+        <v>0.01368428011792811</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5732546241637151</v>
+        <v>0.5815977961432506</v>
       </c>
       <c r="S3" t="n">
-        <v>0.01689606040553305</v>
+        <v>0.01400142991863902</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5928431372549019</v>
+        <v>0.5962745098039216</v>
       </c>
       <c r="U3" t="n">
-        <v>0.02243577702541934</v>
+        <v>0.009490074541435302</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5588235294117647</v>
+        <v>0.5776470588235294</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01764705882352943</v>
+        <v>0.008724939396583146</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5637927170868349</v>
+        <v>0.5826666666666667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01958351431853349</v>
+        <v>0.008620317906844888</v>
       </c>
     </row>
     <row r="4">
@@ -744,7 +744,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -756,58 +756,58 @@
         <v>5</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5746979265078813</v>
+        <v>0.5958982673474933</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01671098573689573</v>
+        <v>0.02002542312981489</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5705882352941176</v>
+        <v>0.5858823529411765</v>
       </c>
       <c r="K4" t="n">
-        <v>0.01440876319284219</v>
+        <v>0.01533929977694739</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5726329050759436</v>
+        <v>0.5907999857829177</v>
       </c>
       <c r="M4" t="n">
-        <v>0.01552630722297881</v>
+        <v>0.01672196545285035</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5763085399449037</v>
+        <v>0.6107438016528925</v>
       </c>
       <c r="O4" t="n">
-        <v>0.02132985821933815</v>
+        <v>0.02039777021865928</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5694214876033058</v>
+        <v>0.6079889807162535</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02101623264216045</v>
+        <v>0.02161700809653369</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5685399449035812</v>
+        <v>0.6051239669421487</v>
       </c>
       <c r="S4" t="n">
-        <v>0.02099672399025554</v>
+        <v>0.02062218546769146</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5888235294117646</v>
+        <v>0.5996078431372549</v>
       </c>
       <c r="U4" t="n">
-        <v>0.01674721022634053</v>
+        <v>0.01657413761490524</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5705882352941176</v>
+        <v>0.5858823529411765</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01440876319284219</v>
+        <v>0.01533929977694739</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5742745098039215</v>
+        <v>0.5876078431372549</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.01560419703199935</v>
+        <v>0.0156361945672834</v>
       </c>
     </row>
     <row r="5">
@@ -838,65 +838,65 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5518064396027279</v>
+        <v>0.5818527585423811</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0197235328887144</v>
+        <v>0.01210157119279966</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5388235294117647</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02020654592625613</v>
+        <v>0.01860163329510809</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5452236165817694</v>
+        <v>0.5791272764952883</v>
       </c>
       <c r="M5" t="n">
-        <v>0.01971884177259502</v>
+        <v>0.01519351278168253</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5668044077134986</v>
+        <v>0.584573002754821</v>
       </c>
       <c r="O5" t="n">
-        <v>0.02190364172698239</v>
+        <v>0.02539072294127718</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5476584022038569</v>
+        <v>0.5793388429752067</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02453569788125821</v>
+        <v>0.02384949533116468</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5491223927587564</v>
+        <v>0.5782920110192837</v>
       </c>
       <c r="S5" t="n">
-        <v>0.02276992476299774</v>
+        <v>0.0241470701702456</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5799019607843137</v>
+        <v>0.591764705882353</v>
       </c>
       <c r="U5" t="n">
-        <v>0.01954954568883272</v>
+        <v>0.02043124082604035</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5388235294117647</v>
+        <v>0.5764705882352941</v>
       </c>
       <c r="W5" t="n">
-        <v>0.02020654592625613</v>
+        <v>0.01860163329510809</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5479495798319328</v>
+        <v>0.5796862745098039</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.0192602076293441</v>
+        <v>0.01889772957279617</v>
       </c>
     </row>
     <row r="6">
@@ -934,58 +934,58 @@
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6015430354997375</v>
+        <v>0.5856848245432447</v>
       </c>
       <c r="I6" t="n">
-        <v>0.02233941822238216</v>
+        <v>0.01416379152881814</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5894117647058824</v>
+        <v>0.5788235294117647</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0192416790985837</v>
+        <v>0.01744987879316629</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5954038321822781</v>
+        <v>0.5822112923890993</v>
       </c>
       <c r="M6" t="n">
-        <v>0.02060234514657168</v>
+        <v>0.0154038327499024</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6170798898071624</v>
+        <v>0.5988980716253444</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01370506111717106</v>
+        <v>0.01902123564292454</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6082644628099173</v>
+        <v>0.5958677685950413</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.01716520945418665</v>
+        <v>0.02016389674398375</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6089256198347106</v>
+        <v>0.5932782369146005</v>
       </c>
       <c r="S6" t="n">
-        <v>0.01503031918760192</v>
+        <v>0.01873339004037885</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6094117647058823</v>
+        <v>0.5919607843137256</v>
       </c>
       <c r="U6" t="n">
-        <v>0.01642851769855169</v>
+        <v>0.01722535348746624</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5894117647058824</v>
+        <v>0.5788235294117647</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0192416790985837</v>
+        <v>0.01744987879316629</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5943529411764705</v>
+        <v>0.5800392156862745</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0177325814376939</v>
+        <v>0.01628950407774308</v>
       </c>
     </row>
     <row r="7">
@@ -1011,70 +1011,70 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6015430354997375</v>
+        <v>0.592271820643178</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02233941822238216</v>
+        <v>0.0142702863136994</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5894117647058824</v>
+        <v>0.5811764705882353</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0192416790985837</v>
+        <v>0.01735044847500309</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5954038321822781</v>
+        <v>0.5866623725244176</v>
       </c>
       <c r="M7" t="n">
-        <v>0.02060234514657168</v>
+        <v>0.01570996758987049</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6170798898071624</v>
+        <v>0.5867768595041323</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01370506111717106</v>
+        <v>0.01585518516972632</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6082644628099173</v>
+        <v>0.5809917355371901</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01716520945418665</v>
+        <v>0.01740667566878692</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6089256198347106</v>
+        <v>0.5796694214876033</v>
       </c>
       <c r="S7" t="n">
-        <v>0.01503031918760192</v>
+        <v>0.01606842444687036</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6094117647058823</v>
+        <v>0.5984313725490196</v>
       </c>
       <c r="U7" t="n">
-        <v>0.01642851769855169</v>
+        <v>0.01635522154599352</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5894117647058824</v>
+        <v>0.5811764705882353</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0192416790985837</v>
+        <v>0.01735044847500309</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5943529411764705</v>
+        <v>0.5841176470588235</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0177325814376939</v>
+        <v>0.01646883744196096</v>
       </c>
     </row>
     <row r="8">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1112,58 +1112,58 @@
         <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5923053929249383</v>
+        <v>0.6019623485231669</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01382262782588121</v>
+        <v>0.02535467281503557</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5894117647058824</v>
+        <v>0.5929411764705883</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01131493180098317</v>
+        <v>0.03067859955389481</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5908235870407339</v>
+        <v>0.5973998713174489</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01168310669472389</v>
+        <v>0.02799402939060132</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5994490358126722</v>
+        <v>0.6133608815426996</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01112210977310539</v>
+        <v>0.02124742152357152</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5925619834710745</v>
+        <v>0.6101928374655647</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01229681218769456</v>
+        <v>0.02282099383716368</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5916804407713498</v>
+        <v>0.6076347894529712</v>
       </c>
       <c r="S8" t="n">
-        <v>0.01133400427375002</v>
+        <v>0.02197781796954578</v>
       </c>
       <c r="T8" t="n">
-        <v>0.608235294117647</v>
+        <v>0.6083333333333333</v>
       </c>
       <c r="U8" t="n">
-        <v>0.01177695440819236</v>
+        <v>0.02721802414098383</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5894117647058824</v>
+        <v>0.5929411764705883</v>
       </c>
       <c r="W8" t="n">
-        <v>0.01131493180098317</v>
+        <v>0.03067859955389481</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5929803921568627</v>
+        <v>0.5951652661064426</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.01096935720020186</v>
+        <v>0.02953430255919588</v>
       </c>
     </row>
     <row r="9">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1194,65 +1194,65 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>5</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5923053929249383</v>
+        <v>0.5911917085542685</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01382262782588121</v>
+        <v>0.0173263585246847</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5894117647058824</v>
+        <v>0.583529411764706</v>
       </c>
       <c r="K9" t="n">
-        <v>0.01131493180098317</v>
+        <v>0.01784205986835662</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5908235870407339</v>
+        <v>0.5873199217620493</v>
       </c>
       <c r="M9" t="n">
-        <v>0.01168310669472389</v>
+        <v>0.01725282003409461</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5994490358126722</v>
+        <v>0.5856749311294764</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01112210977310539</v>
+        <v>0.01696509006909334</v>
       </c>
       <c r="P9" t="n">
-        <v>0.5925619834710745</v>
+        <v>0.5815426997245179</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01229681218769456</v>
+        <v>0.01810129091019233</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5916804407713498</v>
+        <v>0.5797245179063361</v>
       </c>
       <c r="S9" t="n">
-        <v>0.01133400427375002</v>
+        <v>0.01747694530629602</v>
       </c>
       <c r="T9" t="n">
-        <v>0.608235294117647</v>
+        <v>0.5982352941176471</v>
       </c>
       <c r="U9" t="n">
-        <v>0.01177695440819236</v>
+        <v>0.01651313365891579</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5894117647058824</v>
+        <v>0.583529411764706</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01131493180098317</v>
+        <v>0.01784205986835662</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5929803921568627</v>
+        <v>0.586078431372549</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.01096935720020186</v>
+        <v>0.01700577733886005</v>
       </c>
     </row>
     <row r="10">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1290,58 +1290,58 @@
         <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6142633067767237</v>
+        <v>0.6018182252413988</v>
       </c>
       <c r="I10" t="n">
-        <v>0.01707452577899938</v>
+        <v>0.01364436888993048</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5894117647058824</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01832048412046755</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6093984433885951</v>
+        <v>0.5953059405008538</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01406682628532503</v>
+        <v>0.009318253135028889</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6234159779614326</v>
+        <v>0.6110192837465565</v>
       </c>
       <c r="O10" t="n">
-        <v>0.01386334726180294</v>
+        <v>0.01000876150114879</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6214876033057851</v>
+        <v>0.6099173553719008</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.01206315925389064</v>
+        <v>0.01340412190160093</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6191735537190083</v>
+        <v>0.6066115702479339</v>
       </c>
       <c r="S10" t="n">
-        <v>0.01272834598887834</v>
+        <v>0.009620203906465223</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6170588235294118</v>
+        <v>0.601764705882353</v>
       </c>
       <c r="U10" t="n">
-        <v>0.01305431824774831</v>
+        <v>0.01052267283529316</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.5894117647058824</v>
       </c>
       <c r="W10" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01832048412046755</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6069803921568627</v>
+        <v>0.5909411764705882</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.01262659843669335</v>
+        <v>0.01315655591238015</v>
       </c>
     </row>
     <row r="11">
@@ -1362,75 +1362,75 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6142633067767237</v>
+        <v>0.6030085695911831</v>
       </c>
       <c r="I11" t="n">
-        <v>0.01707452577899938</v>
+        <v>0.009012797646555357</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.6</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01100487466698223</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6093984433885951</v>
+        <v>0.601400423124405</v>
       </c>
       <c r="M11" t="n">
-        <v>0.01406682628532503</v>
+        <v>0.005197040985567425</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6234159779614326</v>
+        <v>0.6026170798898072</v>
       </c>
       <c r="O11" t="n">
-        <v>0.01386334726180294</v>
+        <v>0.01131658176663562</v>
       </c>
       <c r="P11" t="n">
-        <v>0.6214876033057851</v>
+        <v>0.6005509641873278</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01206315925389064</v>
+        <v>0.01299446436922395</v>
       </c>
       <c r="R11" t="n">
-        <v>0.6191735537190083</v>
+        <v>0.5984887839433294</v>
       </c>
       <c r="S11" t="n">
-        <v>0.01272834598887834</v>
+        <v>0.01209961814073674</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6170588235294118</v>
+        <v>0.6114705882352942</v>
       </c>
       <c r="U11" t="n">
-        <v>0.01305431824774831</v>
+        <v>0.009665692191267672</v>
       </c>
       <c r="V11" t="n">
-        <v>0.6047058823529412</v>
+        <v>0.6</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01341382853057812</v>
+        <v>0.01100487466698223</v>
       </c>
       <c r="X11" t="n">
-        <v>0.6069803921568627</v>
+        <v>0.6020280112044818</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.01262659843669335</v>
+        <v>0.009291988281439581</v>
       </c>
     </row>
     <row r="12">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1468,58 +1468,58 @@
         <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6191060050431599</v>
+        <v>0.6218562983610971</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0146911284029345</v>
+        <v>0.00726733516752217</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.6035294117647059</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.005261336417646588</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6123924381339001</v>
+        <v>0.6125446125000968</v>
       </c>
       <c r="M12" t="n">
-        <v>0.01195812108222937</v>
+        <v>0.005591362704310393</v>
       </c>
       <c r="N12" t="n">
-        <v>0.6123966942148761</v>
+        <v>0.6272727272727272</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0124957778843435</v>
+        <v>0.007644317865295569</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6090909090909091</v>
+        <v>0.6217630853994491</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01300905669765022</v>
+        <v>0.005299003873738715</v>
       </c>
       <c r="R12" t="n">
-        <v>0.606831955922865</v>
+        <v>0.6213774104683195</v>
       </c>
       <c r="S12" t="n">
-        <v>0.01189910455862876</v>
+        <v>0.006578775414540826</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6209803921568626</v>
+        <v>0.6198039215686274</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0123350321470993</v>
+        <v>0.009640799818776103</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.6035294117647059</v>
       </c>
       <c r="W12" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.005261336417646588</v>
       </c>
       <c r="X12" t="n">
-        <v>0.6087058823529412</v>
+        <v>0.6076078431372549</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.01055331933656936</v>
+        <v>0.007412698353893368</v>
       </c>
     </row>
     <row r="13">
@@ -1550,65 +1550,65 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>5</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6191060050431599</v>
+        <v>0.6182860257151755</v>
       </c>
       <c r="I13" t="n">
-        <v>0.0146911284029345</v>
+        <v>0.01535223929642305</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.6094117647058823</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.009843059135695055</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6123924381339001</v>
+        <v>0.6137869266533855</v>
       </c>
       <c r="M13" t="n">
-        <v>0.01195812108222937</v>
+        <v>0.01188959822147086</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6123966942148761</v>
+        <v>0.6140495867768595</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0124957778843435</v>
+        <v>0.01166334056750226</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6090909090909091</v>
+        <v>0.6157024793388429</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.01300905669765022</v>
+        <v>0.01160626690520161</v>
       </c>
       <c r="R13" t="n">
-        <v>0.606831955922865</v>
+        <v>0.6111294765840221</v>
       </c>
       <c r="S13" t="n">
-        <v>0.01189910455862876</v>
+        <v>0.01143599137047699</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6209803921568626</v>
+        <v>0.6186274509803922</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0123350321470993</v>
+        <v>0.01247835496211553</v>
       </c>
       <c r="V13" t="n">
-        <v>0.6058823529411764</v>
+        <v>0.6094117647058823</v>
       </c>
       <c r="W13" t="n">
-        <v>0.0110048746669822</v>
+        <v>0.009843059135695055</v>
       </c>
       <c r="X13" t="n">
-        <v>0.6087058823529412</v>
+        <v>0.6098823529411764</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.01055331933656936</v>
+        <v>0.01111057284355564</v>
       </c>
     </row>
     <row r="14">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1643,61 +1643,61 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6142652596272505</v>
+        <v>0.613635384990548</v>
       </c>
       <c r="I14" t="n">
-        <v>0.008051003944109524</v>
+        <v>0.0163169637753299</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6088235294117647</v>
+        <v>0.6070588235294118</v>
       </c>
       <c r="K14" t="n">
-        <v>0.01018853416216988</v>
+        <v>0.01275263728745812</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6115091512764134</v>
+        <v>0.6103221397392681</v>
       </c>
       <c r="M14" t="n">
-        <v>0.00811196840080511</v>
+        <v>0.01443043362604954</v>
       </c>
       <c r="N14" t="n">
-        <v>0.6294765840220385</v>
+        <v>0.6267217630853994</v>
       </c>
       <c r="O14" t="n">
-        <v>0.004637054608981692</v>
+        <v>0.01346062003146829</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6336088154269972</v>
+        <v>0.6258953168044077</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.007023442856188429</v>
+        <v>0.01611040387571729</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6284435261707988</v>
+        <v>0.6224793388429751</v>
       </c>
       <c r="S14" t="n">
-        <v>0.005286457592946406</v>
+        <v>0.01520351707245162</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6105392156862746</v>
+        <v>0.6168627450980392</v>
       </c>
       <c r="U14" t="n">
-        <v>0.01116026229838511</v>
+        <v>0.01054548377217634</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6088235294117647</v>
+        <v>0.6070588235294118</v>
       </c>
       <c r="W14" t="n">
-        <v>0.01018853416216988</v>
+        <v>0.01275263728745812</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6064705882352941</v>
+        <v>0.6074117647058823</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.009756749258529211</v>
+        <v>0.0123064796965707</v>
       </c>
     </row>
     <row r="15">
@@ -1718,75 +1718,75 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="n">
         <v>5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6161180900547416</v>
+        <v>0.60829405134835</v>
       </c>
       <c r="I15" t="n">
-        <v>0.008110419307670447</v>
+        <v>0.007878984809884587</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6117647058823529</v>
+        <v>0.6047058823529412</v>
       </c>
       <c r="K15" t="n">
-        <v>0.01100487466698223</v>
+        <v>0.007669649888473703</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6139132033740718</v>
+        <v>0.6064904147761634</v>
       </c>
       <c r="M15" t="n">
-        <v>0.008845923125543572</v>
+        <v>0.007564594131464255</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6314049586776859</v>
+        <v>0.6055096418732783</v>
       </c>
       <c r="O15" t="n">
-        <v>0.005892355271682484</v>
+        <v>0.01154891119352873</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6347107438016528</v>
+        <v>0.6046831955922864</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.006562605647146912</v>
+        <v>0.01140010010829669</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6297520661157023</v>
+        <v>0.6014325068870522</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005433356177222039</v>
+        <v>0.01137410820612044</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6149019607843137</v>
+        <v>0.6145098039215686</v>
       </c>
       <c r="U15" t="n">
-        <v>0.0137324912116809</v>
+        <v>0.008155542879641311</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6117647058823529</v>
+        <v>0.6047058823529412</v>
       </c>
       <c r="W15" t="n">
-        <v>0.01100487466698223</v>
+        <v>0.007669649888473703</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6098823529411764</v>
+        <v>0.6054117647058823</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.01138403746971526</v>
+        <v>0.007416846478646551</v>
       </c>
     </row>
     <row r="16">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1824,58 +1824,58 @@
         <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6204715166401845</v>
+        <v>0.621098320461014</v>
       </c>
       <c r="I16" t="n">
-        <v>0.008102275685873442</v>
+        <v>0.01626971305810327</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6094117647058823</v>
+        <v>0.6047058823529412</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00526133641764661</v>
+        <v>0.006443794794178445</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6148484005176831</v>
+        <v>0.6127023591149782</v>
       </c>
       <c r="M16" t="n">
-        <v>0.003568416526102522</v>
+        <v>0.008944602870055867</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6104683195592286</v>
+        <v>0.6327823691460055</v>
       </c>
       <c r="O16" t="n">
-        <v>0.008623953632230612</v>
+        <v>0.01727538522877482</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6115702479338843</v>
+        <v>0.631129476584022</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01148301101965086</v>
+        <v>0.008894702088684812</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6069500196772923</v>
+        <v>0.6280991735537189</v>
       </c>
       <c r="S16" t="n">
-        <v>0.008627302351816017</v>
+        <v>0.01272446989518573</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6168627450980392</v>
+        <v>0.617843137254902</v>
       </c>
       <c r="U16" t="n">
-        <v>0.01183394657020111</v>
+        <v>0.01308740909487466</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6094117647058823</v>
+        <v>0.6047058823529412</v>
       </c>
       <c r="W16" t="n">
-        <v>0.00526133641764661</v>
+        <v>0.006443794794178445</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6087226890756302</v>
+        <v>0.6059607843137255</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.005750271159191041</v>
+        <v>0.00707460110371071</v>
       </c>
     </row>
     <row r="17">
@@ -1906,65 +1906,65 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6204715166401845</v>
+        <v>0.6194884391449629</v>
       </c>
       <c r="I17" t="n">
-        <v>0.008102275685873442</v>
+        <v>0.01587329900958448</v>
       </c>
       <c r="J17" t="n">
-        <v>0.6094117647058823</v>
+        <v>0.6047058823529412</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00526133641764661</v>
+        <v>0.01052267283529315</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6148484005176831</v>
+        <v>0.61194464811287</v>
       </c>
       <c r="M17" t="n">
-        <v>0.003568416526102522</v>
+        <v>0.01137348290448046</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6104683195592286</v>
+        <v>0.6110192837465565</v>
       </c>
       <c r="O17" t="n">
-        <v>0.008623953632230612</v>
+        <v>0.01663191057644469</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6115702479338843</v>
+        <v>0.6096418732782369</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01148301101965086</v>
+        <v>0.01841819796192484</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6069500196772923</v>
+        <v>0.6067217630853994</v>
       </c>
       <c r="S17" t="n">
-        <v>0.008627302351816017</v>
+        <v>0.01757221654009979</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6168627450980392</v>
+        <v>0.6152941176470588</v>
       </c>
       <c r="U17" t="n">
-        <v>0.01183394657020111</v>
+        <v>0.01064075572644325</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6094117647058823</v>
+        <v>0.6047058823529412</v>
       </c>
       <c r="W17" t="n">
-        <v>0.00526133641764661</v>
+        <v>0.01052267283529315</v>
       </c>
       <c r="X17" t="n">
-        <v>0.6087226890756302</v>
+        <v>0.6058823529411764</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.005750271159191041</v>
+        <v>0.009932490307383506</v>
       </c>
     </row>
   </sheetData>
